--- a/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4925" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4924" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>As Organization Profile</t>
+    <t>AS Organization Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource FrOrganization dans le contexte de l'Annuaire Santé pour décrire les organismes du domaine sanitaire, médico-social et social immatriculés dans le fichier national des établissements sanitaires et sociaux (FINESS) ou dans le Système Informatique pour le Répertoire des Entreprises et de leurs Établissements (SIRENE) dédié aux entreprises, associations et organismes du secteur public.</t>
+    <t>Profil créé à partir de FrOrganization dans le contexte de l'Annuaire Santé pour décrire les organismes du domaine sanitaire, médico-social et social immatriculés dans le fichier national des établissements sanitaires et sociaux (FINESS) ou dans le Système Informatique pour le Répertoire des Entreprises et de leurs Établissements (SIRENE) dédié aux entreprises, associations et organismes du secteur public.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -672,13 +672,10 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Une instance par identifiant (FINESS, SIREN, SIRET, idNat_Struct…).</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
-  </si>
-  <si>
-    <t>Une instance par identifiant (FINESS, SIREN, SIRET, idNat_Struct…)</t>
   </si>
   <si>
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
@@ -731,13 +728,14 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Les codes FINEJ, FINEG, SIREN, SIRET, IDNST, INTRN proviennent de la terminologie  http://interopsante.org/CodeSystem/fr-v2-0203 
+ Les codes 0,4 proviennent de la terminologie TRE-G07-TypeIdentifiantStructure.</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>Les codes FINEJ, FINEG, SIREN, SIRET, IDNST, INTRN proviennent du system  http://interopsante.org/CodeSystem/fr-v2-0203 ; Les codes 0,4 proviennent du system https://mos.esante.gouv.fr/NOS/TRE_G07-TypeIdentifiantStructure/FHIR/TRE-G07-TypeIdentifiantStructure</t>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
@@ -755,16 +753,29 @@
     <t>Identifier.type</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-bind-type:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
+ fr-organization-identifier-type , URL : http://interopsante.org/CodeSystem/fr-v2-0203
+ TRE_G07-TypeIdentifiantStructure , OID : 1.2.250.1.71.1.2.14 
+ JDV_J104-TypeIdentifiantStructure-RASS , OID : 1.2.250.1.213.1.6.1.172
+Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : fr-organization-identifier-type ).
+En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J104-TypeIdentifiantStructure-RASS peut être utilisé. {f:type}</t>
+  </si>
+  <si>
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>« urn:oid:1.2.250.1.71.4.2.2 » si l’instance correspond à l’identification nationale des structures (idNat_Struct)
+ « http://sirene.fr» si l’instance correspond à un identifiant SIREN ou SIRET 
+ « http://finess.sante.gouv.fr» si l’instance correspond à un identifiant FINESS EG ou EJ 
+ « urn:oid:1.2.250.1.213.1.6.4.3 » si l’instance correspond à un identifiant ADELI rang ou RPPS rang
+« https://annuaire.sante.fr » si l’instance correspond à l’identifiant technique de la structure.</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>« urn:oid:1.2.250.1.71.4.2.2 » si l’instance correspond à l’identification nationale des structures (idNat_Struct) ; « http://sirene.fr» si l’instance correspond à un identifiant SIREN ou SIRET ; « http://finess.sante.gouv.fr» si l’instance correspond à un identifiant FINESS EG ou EJ ; « urn:oid:1.2.250.1.213.1.6.4.3 » si l’instance correspond à un identifiant ADELI rang ou RPPS rang; « https://annuaire.sante.fr » si l’instance correspond à l’identifiant technique de la structure;</t>
+    <t>Identifier.system is always case sensitive.</t>
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
@@ -779,7 +790,7 @@
     <t>Organization.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>Identification nationale de la structure, Numéro SIRET, Numéro SIREN, Numéro FINESS Etablissement, Numéro FINESS EJ, RPPS rang, ADELI rang, Identifiant technique de la structure.</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -850,7 +861,7 @@
     <t>Whether the organization's record is still in active use.</t>
   </si>
   <si>
-    <t>true par défaut; false pour les structures supprimées</t>
+    <t>true par défaut; false pour les structures supprimées.</t>
   </si>
   <si>
     <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
@@ -1688,7 +1699,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeBAL 
+    <t>Synonyme : typeBAL 
 Valeurs possibles :
 ORG pour une BAL organisationnelle;
 APP pour une BAL applicative;
@@ -1740,7 +1751,7 @@
     <t>Description fonctionnelle de la boîte aux lettres.</t>
   </si>
   <si>
-    <t>Synonyme MOS : description</t>
+    <t>Synonyme : description</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
@@ -1788,7 +1799,7 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
-    <t>Synonyme MOS : serviceRattachement</t>
+    <t>Synonyme : serviceRattachement</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
@@ -1837,7 +1848,7 @@
 - N : Dématérialisation refusée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dematerialisation</t>
+    <t>Synonyme : dematerialisation</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
@@ -1862,7 +1873,7 @@
 N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
-    <t>Synonyme MOS : listeRouge</t>
+    <t>Synonyme : listeRouge</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:publication.id</t>
@@ -4808,11 +4819,9 @@
       <c r="M25" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
@@ -4870,7 +4879,7 @@
         <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>91</v>
@@ -4878,10 +4887,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4978,10 +4987,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5080,10 +5089,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5109,65 +5118,65 @@
         <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X28" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X28" t="s" s="2">
+      <c r="Y28" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
@@ -5184,10 +5193,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5210,19 +5219,19 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
@@ -5247,31 +5256,31 @@
         <v>71</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y29" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -5283,7 +5292,7 @@
         <v>90</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>91</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5830,7 +5839,7 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>270</v>
@@ -5934,7 +5943,7 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>280</v>
@@ -5971,7 +5980,7 @@
         <v>71</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>275</v>
@@ -7170,7 +7179,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>270</v>
@@ -7207,7 +7216,7 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>342</v>
@@ -8406,7 +8415,7 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>270</v>
@@ -8443,7 +8452,7 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>359</v>
@@ -9642,7 +9651,7 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>376</v>
@@ -9679,7 +9688,7 @@
         <v>71</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
@@ -9746,7 +9755,7 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>381</v>
@@ -9783,7 +9792,7 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
@@ -9850,7 +9859,7 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>386</v>
@@ -9887,7 +9896,7 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
@@ -10022,7 +10031,7 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>91</v>
@@ -10605,7 +10614,7 @@
         <v>71</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y81" t="s" s="2">
         <v>417</v>
@@ -10813,7 +10822,7 @@
         <v>71</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y83" t="s" s="2">
         <v>432</v>
@@ -11631,7 +11640,7 @@
         <v>71</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y91" t="s" s="2">
         <v>471</v>
@@ -12312,7 +12321,7 @@
         <v>71</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>497</v>
@@ -12349,7 +12358,7 @@
         <v>71</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y98" t="s" s="2">
         <v>501</v>
@@ -13740,7 +13749,7 @@
         <v>71</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>164</v>
@@ -13840,7 +13849,7 @@
         <v>71</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>164</v>
@@ -13873,7 +13882,7 @@
         <v>71</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y113" t="s" s="2">
         <v>547</v>
@@ -17213,7 +17222,7 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y146" t="s" s="2">
         <v>417</v>
@@ -17421,7 +17430,7 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y148" t="s" s="2">
         <v>432</v>
@@ -17599,7 +17608,7 @@
         <v>443</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>444</v>
+        <v>252</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">

--- a/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17608,7 +17608,7 @@
         <v>443</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>252</v>
+        <v>444</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">

--- a/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
